--- a/Plantilla_Reportes_POB.xlsx
+++ b/Plantilla_Reportes_POB.xlsx
@@ -805,7 +805,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>INTERNO</t>
+          <t>INGRESO</t>
         </is>
       </c>
     </row>
@@ -822,7 +822,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>INTERNO</t>
+          <t>EGRESO</t>
         </is>
       </c>
     </row>
@@ -839,7 +839,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>INTERNO</t>
+          <t>INGRESO</t>
         </is>
       </c>
     </row>
@@ -856,7 +856,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>INTERNO</t>
+          <t>EGRESO</t>
         </is>
       </c>
     </row>
@@ -873,7 +873,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>INTERNO</t>
+          <t>INGRESO</t>
         </is>
       </c>
     </row>
@@ -890,7 +890,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>INTERNO</t>
+          <t>EGRESO</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>INTERNO</t>
+          <t>EGRESO</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>INTERNO</t>
+          <t>INGRESO</t>
         </is>
       </c>
     </row>
@@ -1250,7 +1250,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>INTERNO</t>
+          <t>INGRESO</t>
         </is>
       </c>
     </row>
@@ -1262,7 +1262,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>INTERNO</t>
+          <t>INGRESO</t>
         </is>
       </c>
     </row>
@@ -1274,7 +1274,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>INTERNO</t>
+          <t>EGRESO</t>
         </is>
       </c>
     </row>
@@ -1291,7 +1291,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>INTERNO</t>
+          <t>INGRESO</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>INTERNO</t>
+          <t>EGRESO</t>
         </is>
       </c>
     </row>
@@ -1345,7 +1345,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>INTERNO</t>
+          <t>INGRESO</t>
         </is>
       </c>
     </row>
@@ -1372,7 +1372,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>INTERNO</t>
+          <t>EGRESO</t>
         </is>
       </c>
     </row>
@@ -1399,7 +1399,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>INTERNO</t>
+          <t>INGRESO</t>
         </is>
       </c>
     </row>
@@ -1426,7 +1426,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>INTERNO</t>
+          <t>EGRESO</t>
         </is>
       </c>
     </row>
@@ -1438,7 +1438,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>INTERNO</t>
+          <t>INGRESO</t>
         </is>
       </c>
     </row>
@@ -1450,7 +1450,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>INTERNO</t>
+          <t>EGRESO</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>INTERNO</t>
+          <t>EGRESO</t>
         </is>
       </c>
     </row>
@@ -1902,7 +1902,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>INTERNO</t>
+          <t>EGRESO</t>
         </is>
       </c>
     </row>
@@ -1914,7 +1914,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>INTERNO</t>
+          <t>EGRESO</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>INTERNO</t>
+          <t>EGRESO</t>
         </is>
       </c>
     </row>
@@ -1938,7 +1938,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>INTERNO</t>
+          <t>EGRESO</t>
         </is>
       </c>
     </row>
@@ -1950,7 +1950,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>INTERNO</t>
+          <t>EGRESO</t>
         </is>
       </c>
     </row>
@@ -1962,7 +1962,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>INTERNO</t>
+          <t>EGRESO</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>INTERNO</t>
+          <t>EGRESO</t>
         </is>
       </c>
     </row>
@@ -1986,7 +1986,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>INTERNO</t>
+          <t>EGRESO</t>
         </is>
       </c>
     </row>
@@ -1998,7 +1998,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>INTERNO</t>
+          <t>EGRESO</t>
         </is>
       </c>
     </row>
@@ -2010,7 +2010,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>INTERNO</t>
+          <t>EGRESO</t>
         </is>
       </c>
     </row>
@@ -2022,7 +2022,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>INTERNO</t>
+          <t>EGRESO</t>
         </is>
       </c>
     </row>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>INTERNO</t>
+          <t>EGRESO</t>
         </is>
       </c>
     </row>
@@ -2046,7 +2046,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>INTERNO</t>
+          <t>EGRESO</t>
         </is>
       </c>
     </row>
@@ -2058,7 +2058,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>INTERNO</t>
+          <t>EGRESO</t>
         </is>
       </c>
     </row>
@@ -2070,7 +2070,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>INTERNO</t>
+          <t>EGRESO</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>INTERNO</t>
+          <t>EGRESO</t>
         </is>
       </c>
     </row>
